--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПГД/ОБЩИНА ВАРНА % 5 - ПГД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПГД/ОБЩИНА ВАРНА % 5 - ПГД.xlsx
@@ -103,7 +103,7 @@
     <t>15:53</t>
   </si>
   <si>
-    <t>Общи литри по продукт / ОБЩИНА ВАРНА % 5 - ПГД</t>
+    <t>Общи литри по продукт / ОБЩИНА ВАРНА % 5 - ПГД</t>
   </si>
   <si>
     <t>Продукт</t>
